--- a/AAII_Financials/Quarterly/DTTLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DTTLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>DTTLY</t>
   </si>
@@ -2151,10 +2151,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2420400</v>
+        <v>2380000</v>
       </c>
       <c r="E43" s="3">
-        <v>2420400</v>
+        <v>2380000</v>
       </c>
       <c r="F43" s="3">
         <v>2059700</v>
@@ -2244,11 +2244,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>42800</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -2574,10 +2574,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>521400</v>
+        <v>65800</v>
       </c>
       <c r="E52" s="3">
-        <v>521400</v>
+        <v>65800</v>
       </c>
       <c r="F52" s="3">
         <v>488300</v>
@@ -2586,10 +2586,10 @@
         <v>488300</v>
       </c>
       <c r="H52" s="3">
-        <v>42400</v>
+        <v>42600</v>
       </c>
       <c r="I52" s="3">
-        <v>42400</v>
+        <v>42600</v>
       </c>
       <c r="J52" s="3">
         <v>266500</v>
@@ -2753,10 +2753,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2561500</v>
+        <v>1895800</v>
       </c>
       <c r="E57" s="3">
-        <v>2561500</v>
+        <v>1895800</v>
       </c>
       <c r="F57" s="3">
         <v>2482300</v>
@@ -2765,10 +2765,10 @@
         <v>2482300</v>
       </c>
       <c r="H57" s="3">
-        <v>1684000</v>
+        <v>1670500</v>
       </c>
       <c r="I57" s="3">
-        <v>1684000</v>
+        <v>1670500</v>
       </c>
       <c r="J57" s="3">
         <v>1544600</v>
@@ -2847,10 +2847,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>269200</v>
+        <v>868200</v>
       </c>
       <c r="E59" s="3">
-        <v>269200</v>
+        <v>868200</v>
       </c>
       <c r="F59" s="3">
         <v>217000</v>
@@ -2859,10 +2859,10 @@
         <v>217000</v>
       </c>
       <c r="H59" s="3">
-        <v>640800</v>
+        <v>658100</v>
       </c>
       <c r="I59" s="3">
-        <v>640800</v>
+        <v>658100</v>
       </c>
       <c r="J59" s="3">
         <v>714800</v>
@@ -2988,10 +2988,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>405100</v>
+        <v>401300</v>
       </c>
       <c r="E62" s="3">
-        <v>405100</v>
+        <v>401300</v>
       </c>
       <c r="F62" s="3">
         <v>364400</v>
@@ -3000,10 +3000,10 @@
         <v>364400</v>
       </c>
       <c r="H62" s="3">
-        <v>267400</v>
+        <v>270700</v>
       </c>
       <c r="I62" s="3">
-        <v>267400</v>
+        <v>270700</v>
       </c>
       <c r="J62" s="3">
         <v>194800</v>
@@ -4178,10 +4178,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9600</v>
+        <v>-3500</v>
       </c>
       <c r="E91" s="3">
-        <v>-9600</v>
+        <v>-3500</v>
       </c>
       <c r="F91" s="3">
         <v>-2600</v>
